--- a/templates/000_pm_suite/01_프로젝트 관리/06_조직관리/프로젝트명_인력투입계획서_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/01_프로젝트 관리/06_조직관리/프로젝트명_인력투입계획서_V1.0_20230530.xlsx
@@ -634,7 +634,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 프로젝트 개요</t>
+          <t>SyncFlow AI 시스템 구축 프로젝트 개요</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 용역</t>
+          <t>SyncFlow AI 시스템 구축 용역</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>주식회사 한빛글로벌 (Hanbit Global Corp.) - RA팀</t>
+          <t>주식회사 한빛글로벌 (Hanbit Global Corp.) - QA팀</t>
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>엠파시(AI엔진·백엔드·뷰어·사업관리) + 데이터브릿지(마케팅허브·프로덕트랩 연계) + 한빛글로벌(RA Lab·기술PM)</t>
+          <t>엠파시(AI엔진·백엔드·뷰어·사업관리) + 데이터브릿지(전자구매포털·피엘엠넥서스 연계) + 한빛글로벌(품질법무검증팀·기술PM)</t>
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
@@ -818,7 +818,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>착수 킥오프 완료(2026.10.16), 동영상 장면 캡처·목업 PoC 완료(2026.10.23), 요구사항 확정(2026.11.20 예정)</t>
+          <t>착수 킥오프 완료(2026.10.16), 설계도면 스냅샷 추출·목업 PoC 완료(2026.10.23), 요구사항 확정(2026.11.20 예정)</t>
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>11개 브랜드 142건 시범운영, 교육(22명), 골든셋(96.2%), 최종검수 합격 (2026.10.16)</t>
+          <t>11개 사업본부 142건 시범운영, 교육(22명), 골든셋(96.2%), 최종검수 합격 (2026.10.16)</t>
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
@@ -914,7 +914,7 @@
     <row r="2">
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>SyncGuard AI 월별 인력 투입 및 공수 집계표</t>
+          <t>SyncFlow AI 월별 인력 투입 및 공수 집계표</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>동영상 장면 캡처·긴 JPG PoC</t>
+          <t>설계도면 스냅샷 추출·긴 JPG PoC</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>마케팅허브·프로덕트랩 연계 프로토타입 UI</t>
+          <t>전자구매포털·피엘엠넥서스 연계 프로토타입 UI</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>착수 킥오프, 현업 인터뷰, 동영상·목업 PoC, 요구사항·연계규격 확정</t>
+          <t>착수 킥오프, 현업 인터뷰, 설계도면·목업 PoC, 요구사항·연계규격 확정</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AWS EC2 아키텍처 정의, 화면/DB/마케팅허브·프로덕트랩 연계 상세 설계</t>
+          <t>AWS EC2 아키텍처 정의, 화면/DB/전자구매포털·피엘엠넥서스 연계 상세 설계</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>3단계 AI 판정·RAG, 동영상 장면 캡처 뷰어, 기간계 연계 본 개발</t>
+          <t>3단계 AI 판정·RAG, 설계도면 스냅샷 추출 뷰어, 기간계 연계 본 개발</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>착수 킥오프, 현업 인터뷰, 동영상·목업 PoC, 요구사항·연계규격 확정</t>
+          <t>착수 킥오프, 현업 인터뷰, 설계도면·목업 PoC, 요구사항·연계규격 확정</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AWS EC2 아키텍처 정의, 화면/DB/마케팅허브·프로덕트랩 연계 상세 설계</t>
+          <t>AWS EC2 아키텍처 정의, 화면/DB/전자구매포털·피엘엠넥서스 연계 상세 설계</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>3단계 AI 판정·RAG, 동영상 장면 캡처 뷰어, 기간계 연계 본 개발</t>
+          <t>3단계 AI 판정·RAG, 설계도면 스냅샷 추출 뷰어, 기간계 연계 본 개발</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>담당 업무: 식약처 표시·광고 공정화법 제3조 100개 룰셋 DB화, 프롬프트 15종 명세 작성, 골든셋 50문항 튜닝</t>
+          <t>담당 업무: 공정위·표준원 하도급법 제3조의4 100개 룰셋 DB화, 프롬프트 15종 명세 작성, 골든셋 50문항 튜닝</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>착수 킥오프, 현업 인터뷰, 동영상·목업 PoC, 요구사항·연계규격 확정</t>
+          <t>착수 킥오프, 현업 인터뷰, 설계도면·목업 PoC, 요구사항·연계규격 확정</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AWS EC2 아키텍처 정의, 화면/DB/마케팅허브·프로덕트랩 연계 상세 설계</t>
+          <t>AWS EC2 아키텍처 정의, 화면/DB/전자구매포털·피엘엠넥서스 연계 상세 설계</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>3단계 AI 판정·RAG, 동영상 장면 캡처 뷰어, 기간계 연계 본 개발</t>
+          <t>3단계 AI 판정·RAG, 설계도면 스냅샷 추출 뷰어, 기간계 연계 본 개발</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>담당 업무: Spring Boot 3.3.5 코어 API 구축, ProductLab 원료 규격 REST API 연계, SSO/MarketingHub 인터페이스</t>
+          <t>담당 업무: Spring Boot 3.3.5 코어 API 구축, PLM-Nexus 원소재 규격 REST API 연계, SSO/SRM-Portal 인터페이스</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>착수 킥오프, 현업 인터뷰, 동영상·목업 PoC, 요구사항·연계규격 확정</t>
+          <t>착수 킥오프, 현업 인터뷰, 설계도면·목업 PoC, 요구사항·연계규격 확정</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AWS EC2 아키텍처 정의, 화면/DB/마케팅허브·프로덕트랩 연계 상세 설계</t>
+          <t>AWS EC2 아키텍처 정의, 화면/DB/전자구매포털·피엘엠넥서스 연계 상세 설계</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>3단계 AI 판정·RAG, 동영상 장면 캡처 뷰어, 기간계 연계 본 개발</t>
+          <t>3단계 AI 판정·RAG, 설계도면 스냅샷 추출 뷰어, 기간계 연계 본 개발</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>담당 업무: Vben Admin 기반 반응형 UI, 캔버스 시안 대조 슬라이더 뷰어, 심의 피드백 및 결재 대시보드</t>
+          <t>담당 업무: Vben Admin 기반 반응형 UI, 캔버스 계약·도서 대조 슬라이더 뷰어, 검증 피드백 및 결재 대시보드</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>착수 킥오프, 현업 인터뷰, 동영상·목업 PoC, 요구사항·연계규격 확정</t>
+          <t>착수 킥오프, 현업 인터뷰, 설계도면·목업 PoC, 요구사항·연계규격 확정</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AWS EC2 아키텍처 정의, 화면/DB/마케팅허브·프로덕트랩 연계 상세 설계</t>
+          <t>AWS EC2 아키텍처 정의, 화면/DB/전자구매포털·피엘엠넥서스 연계 상세 설계</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>3단계 AI 판정·RAG, 동영상 장면 캡처 뷰어, 기간계 연계 본 개발</t>
+          <t>3단계 AI 판정·RAG, 설계도면 스냅샷 추출 뷰어, 기간계 연계 본 개발</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>착수 킥오프, 현업 인터뷰, 동영상·목업 PoC, 요구사항·연계규격 확정</t>
+          <t>착수 킥오프, 현업 인터뷰, 설계도면·목업 PoC, 요구사항·연계규격 확정</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AWS EC2 아키텍처 정의, 화면/DB/마케팅허브·프로덕트랩 연계 상세 설계</t>
+          <t>AWS EC2 아키텍처 정의, 화면/DB/전자구매포털·피엘엠넥서스 연계 상세 설계</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>3단계 AI 판정·RAG, 동영상 장면 캡처 뷰어, 기간계 연계 본 개발</t>
+          <t>3단계 AI 판정·RAG, 설계도면 스냅샷 추출 뷰어, 기간계 연계 본 개발</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
